--- a/AAII_Financials/Quarterly/YMAT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/YMAT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
   <si>
     <t>YMAT</t>
   </si>
@@ -1084,10 +1084,10 @@
         <v>-300</v>
       </c>
       <c r="F20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
         <v>0</v>
@@ -1119,10 +1119,10 @@
         <v>-10000</v>
       </c>
       <c r="F21" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G21" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="H21" s="3">
         <v>300</v>
@@ -1154,10 +1154,10 @@
         <v>100</v>
       </c>
       <c r="F22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H22" s="3">
         <v>100</v>
@@ -1504,10 +1504,10 @@
         <v>300</v>
       </c>
       <c r="F32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
         <v>0</v>
@@ -1743,10 +1743,10 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -1848,10 +1848,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="E45" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="F45" s="3">
         <v>2300</v>
@@ -2298,10 +2298,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="E59" s="3">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="F59" s="3">
         <v>200</v>
@@ -3251,8 +3251,8 @@
       <c r="F89" s="3">
         <v>-1200</v>
       </c>
-      <c r="G89" s="3">
-        <v>-1200</v>
+      <c r="G89" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H89" s="3">
         <v>-300</v>
@@ -3301,8 +3301,8 @@
       <c r="F91" s="3">
         <v>0</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
+      <c r="G91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
@@ -3406,8 +3406,8 @@
       <c r="F94" s="3">
         <v>900</v>
       </c>
-      <c r="G94" s="3">
-        <v>900</v>
+      <c r="G94" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H94" s="3">
         <v>0</v>
@@ -3596,8 +3596,8 @@
       <c r="F100" s="3">
         <v>100</v>
       </c>
-      <c r="G100" s="3">
-        <v>100</v>
+      <c r="G100" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H100" s="3">
         <v>600</v>
@@ -3667,7 +3667,7 @@
         <v>-200</v>
       </c>
       <c r="G102" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="H102" s="3">
         <v>300</v>
